--- a/data/ragasTest/testRagas.xlsx
+++ b/data/ragasTest/testRagas.xlsx
@@ -471,32 +471,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Combien de temps dure l'évènement de PROVALP 3D à Nice ?</t>
+          <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['[{\'id\': 76804754, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'51501cc970790e7fba85ecdae63bc596\'}, {\'id\': 6940499, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'0b7e60eea3635675753ea6e8821be9cc\'}]']</t>
+          <t>['[]']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L'événement de PROVALP 3D à Nice dure **3 heures**.</t>
+          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D à Nice dure 3 heures (de 9h00 à 12h00 environ).</t>
+          <t>2 évènements se sont déroulé le 25 aout 2025 à Nice, le premier : comment mobiliser vos applications France Travail, le deuxième : atelier le héros aux mille et un visage avec Dany Albiach</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9999999999</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -505,32 +505,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>quel évènement se sont produit le 25 août 2025 à Nice ?</t>
+          <t>Combien de temps dure l'évènement de PROVALP 3D à Nice ?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['[]']</t>
+          <t>['[{\'id\': 76804754, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'1 jeune  1 solution\' \'Recrutement\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'51501cc970790e7fba85ecdae63bc596\'}, {\'id\': 6940499, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;PROVALP 3D spécialisé dans le secteur de la désinfection , désinsectisation et dératisation vient présenter ses recrutements. Emploi propre , sans port de charge lourde, le/la  technicien/ne  en gestion des nuisible est formée en INTERNE. Seul prérequis LE PERMIS B  OBLIGATOIRE.Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;\\n&lt;p&gt;Présentation de PROVALP 3D Seul prérequis LE PERMIS B  OBLIGATOIRE. Se présenter avec un CV le 3 septembre à 9h00 et prévoyez la matinée.&lt;/p&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Agence NICE NORD, 06100 Nice&lt;br&gt;- L\'évènement aura lieu à la date suivante : 03-September-2025 09:00:00&lt;br&gt;- l\'évènement durera : 0 days 03:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : [\'Job dating\' \'1 jeune  1 solution\' \'Recrutement\' \'Tout public\' \'CDI\'\\n \'en physique\']},{ accessibilite : none},{ coordonnees : {\'lon\': 7.262505, \'lat\': 43.714504}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'0b7e60eea3635675753ea6e8821be9cc\'}]']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Aucun événement ne s'est produit le 25 août 2025 à Nice selon le contexte fourni.</t>
+          <t>L'événement de PROVALP 3D à Nice dure **3 heures**.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 évènements se sont déroulé le 25 aout 2025 à Nice, le premier : comment mobiliser vos applications France Travail, le deuxième : atelier le héros aux mille et un visage avec Dany Albiach</t>
+          <t>L'évènement de recrutement de PROVALP 3D à Nice dure 3 heures (de 9h00 à 12h00 environ).</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.9999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +549,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence Nice Nord (06100 Nice). Il est conseillé de prévoir la matinée.</t>
+          <t>L'évènement de recrutement de PROVALP 3D se déroule le **3 septembre 2025 à 9h00** à l'Agence NICE NORD, 06100 Nice. Il est conseillé de prévoir la matinée.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -578,12 +578,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['[]']</t>
+          <t>['[{\'id\': 21312701, \'text\': "&lt;h1&gt;Description de l\'évènement : &lt;/h1&gt;&lt;p&gt;La conférence « Terre &amp;amp; Ciel » est destinée à une trentaine de vos élèves et est entièrement prise en charge par notre association Aérométiers. Elle vise à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale, durant 2 heures. Cette conférence interactive permet aux jeunes de réfléchir à leur orientation professionnelle.&lt;br&gt;Pour garantir le bon déroulement de la conférence, certaines conditions doivent être respectées :&lt;/p&gt;\\n&lt;ul&gt;\\n&lt;li&gt;1. 15 élèves minimum - 30 élèves maximum&lt;/li&gt;\\n&lt;li&gt;2. Un format de 2 heures&lt;/li&gt;\\n&lt;li&gt;3. Une salle dédiée&lt;/li&gt;\\n&lt;li&gt;4. La présence d\'un membre de l\'équipe éducative&lt;/li&gt;\\n&lt;li&gt;5. Un tableau, un PC équipé d\'un rétroprojecteur et d\'enceintes pour visionner un PowerPoint et des vidéos.&lt;/li&gt;\\n&lt;/ul&gt;&lt;h1&gt;Informations supplémentaires : &lt;/h1&gt;&lt;p&gt;- Les conditions sont les suivantes : none&lt;br&gt;- L\'évènement se déroule à l\'adresse suivante : Lycée Parc Impérial, 2 avenue paul arène&lt;br&gt;- L\'évènement aura lieu à la date suivante : 26-November-2025 08:00:00&lt;br&gt;- l\'évènement durera : 0 days 02:00:00&lt;/p&gt;", \'metadata\': "[{ motsCles : none},{ accessibilite : none},{ coordonnees : {\'lon\': 7.251804, \'lat\': 43.708985}},{ telephone : none},{ site_web : none}]", \'model\': \'mistral-embed\', \'rowHash\': \'f27d139e712c9c321daa4b4c350e3ba5\'}]']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Aucun évènement ne s'est déroulé au Lycée Parc Impérial à Nice en 2025 selon le contexte fourni.</t>
+          <t>La conférence « Terre &amp; Ciel » destinée à faire découvrir les métiers du secteur aérien ainsi que de l’industrie aéronautique et spatiale s'est déroulée au Lycée Parc Impérial le 26 novembre 2025.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -595,10 +595,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.9999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
